--- a/dataset_t6_grouped/results2/G1/G1_T0374_W0017F0003T0006Z000C1N1_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T0374_W0017F0003T0006Z000C1N1_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>38.7764467022074</v>
+        <v>6.301172589108703</v>
       </c>
       <c r="D2" t="n">
-        <v>40.93485991733603</v>
+        <v>6.651914736567105</v>
       </c>
       <c r="E2" t="n">
-        <v>10.10876518886647</v>
+        <v>1.642674343190802</v>
       </c>
       <c r="F2" t="n">
-        <v>10.79168524793094</v>
+        <v>1.753648852788777</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>35.37615791387538</v>
+        <v>5.74862566100475</v>
       </c>
       <c r="D3" t="n">
-        <v>34.4896949531819</v>
+        <v>5.604575429892059</v>
       </c>
       <c r="E3" t="n">
-        <v>10.10876518886647</v>
+        <v>1.642674343190802</v>
       </c>
       <c r="F3" t="n">
-        <v>10.79168524793094</v>
+        <v>1.753648852788777</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>29.30123547791852</v>
+        <v>4.761450765161759</v>
       </c>
       <c r="D4" t="n">
-        <v>28.24853528472339</v>
+        <v>4.590386983767551</v>
       </c>
       <c r="E4" t="n">
-        <v>10.10876518886647</v>
+        <v>1.642674343190802</v>
       </c>
       <c r="F4" t="n">
-        <v>10.79168524793094</v>
+        <v>1.753648852788777</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>16.97489205500649</v>
+        <v>2.758419958938555</v>
       </c>
       <c r="D5" t="n">
-        <v>19.15236833512237</v>
+        <v>3.112259854457386</v>
       </c>
       <c r="E5" t="n">
-        <v>10.10876518886647</v>
+        <v>1.642674343190802</v>
       </c>
       <c r="F5" t="n">
-        <v>10.79168524793094</v>
+        <v>1.753648852788777</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>13.61758496972906</v>
+        <v>2.212857557580972</v>
       </c>
       <c r="D6" t="n">
-        <v>12.60934860939684</v>
+        <v>2.049019149026987</v>
       </c>
       <c r="E6" t="n">
-        <v>10.10876518886647</v>
+        <v>1.642674343190802</v>
       </c>
       <c r="F6" t="n">
-        <v>10.79168524793094</v>
+        <v>1.753648852788777</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>47.01774244014062</v>
+        <v>7.640383146522852</v>
       </c>
       <c r="D7" t="n">
-        <v>48.07939328836066</v>
+        <v>7.812901409358608</v>
       </c>
       <c r="E7" t="n">
-        <v>10.10876518886647</v>
+        <v>1.642674343190802</v>
       </c>
       <c r="F7" t="n">
-        <v>10.79168524793094</v>
+        <v>1.753648852788777</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>10.45751495570361</v>
+        <v>1.699346180301837</v>
       </c>
       <c r="D8" t="n">
-        <v>12.05599099719105</v>
+        <v>1.959098537043547</v>
       </c>
       <c r="E8" t="n">
-        <v>10.10876518886647</v>
+        <v>1.642674343190802</v>
       </c>
       <c r="F8" t="n">
-        <v>10.79168524793094</v>
+        <v>1.753648852788777</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>29.43234498477332</v>
+        <v>4.782756060025664</v>
       </c>
       <c r="D9" t="n">
-        <v>27.67153082532678</v>
+        <v>4.496623759115602</v>
       </c>
       <c r="E9" t="n">
-        <v>10.10876518886647</v>
+        <v>1.642674343190802</v>
       </c>
       <c r="F9" t="n">
-        <v>10.79168524793094</v>
+        <v>1.753648852788777</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>25.00636247671761</v>
+        <v>4.063533902466612</v>
       </c>
       <c r="D10" t="n">
-        <v>26.93197209034685</v>
+        <v>4.376445464681363</v>
       </c>
       <c r="E10" t="n">
-        <v>10.10876518886647</v>
+        <v>1.642674343190802</v>
       </c>
       <c r="F10" t="n">
-        <v>10.79168524793094</v>
+        <v>1.753648852788777</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>11.00261187858925</v>
+        <v>1.787924430270753</v>
       </c>
       <c r="D11" t="n">
-        <v>12.92964249696965</v>
+        <v>2.101066905757568</v>
       </c>
       <c r="E11" t="n">
-        <v>10.10876518886647</v>
+        <v>1.642674343190802</v>
       </c>
       <c r="F11" t="n">
-        <v>10.79168524793094</v>
+        <v>1.753648852788777</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>38.31396225122276</v>
+        <v>6.226018865823699</v>
       </c>
       <c r="D12" t="n">
-        <v>38.37726344916661</v>
+        <v>6.236305310489575</v>
       </c>
       <c r="E12" t="n">
-        <v>10.10876518886647</v>
+        <v>1.642674343190802</v>
       </c>
       <c r="F12" t="n">
-        <v>10.79168524793094</v>
+        <v>1.753648852788777</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>14.04019299663051</v>
+        <v>2.281531361952458</v>
       </c>
       <c r="D13" t="n">
-        <v>11.87102247757488</v>
+        <v>1.929041152605918</v>
       </c>
       <c r="E13" t="n">
-        <v>10.10876518886647</v>
+        <v>1.642674343190802</v>
       </c>
       <c r="F13" t="n">
-        <v>10.79168524793094</v>
+        <v>1.753648852788777</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>35.63825225142264</v>
+        <v>5.791215990856179</v>
       </c>
       <c r="D14" t="n">
-        <v>35.3263383514097</v>
+        <v>5.740529982104077</v>
       </c>
       <c r="E14" t="n">
-        <v>10.10876518886647</v>
+        <v>1.642674343190802</v>
       </c>
       <c r="F14" t="n">
-        <v>10.79168524793094</v>
+        <v>1.753648852788777</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>30.62065234241839</v>
+        <v>4.975856005642989</v>
       </c>
       <c r="D15" t="n">
-        <v>31.02247915345394</v>
+        <v>5.041152862436266</v>
       </c>
       <c r="E15" t="n">
-        <v>10.10876518886647</v>
+        <v>1.642674343190802</v>
       </c>
       <c r="F15" t="n">
-        <v>10.79168524793094</v>
+        <v>1.753648852788777</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>28.34086185544874</v>
+        <v>4.605390051510421</v>
       </c>
       <c r="D16" t="n">
-        <v>26.16553690261573</v>
+        <v>4.251899746675057</v>
       </c>
       <c r="E16" t="n">
-        <v>10.10876518886647</v>
+        <v>1.642674343190802</v>
       </c>
       <c r="F16" t="n">
-        <v>10.79168524793094</v>
+        <v>1.753648852788777</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>32.08830588269243</v>
+        <v>5.21434970593752</v>
       </c>
       <c r="D17" t="n">
-        <v>31.11237963080864</v>
+        <v>5.055761690006404</v>
       </c>
       <c r="E17" t="n">
-        <v>10.10876518886647</v>
+        <v>1.642674343190802</v>
       </c>
       <c r="F17" t="n">
-        <v>10.79168524793094</v>
+        <v>1.753648852788777</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>19.58727272371627</v>
+        <v>3.182931817603895</v>
       </c>
       <c r="D18" t="n">
-        <v>18.98469331947513</v>
+        <v>3.085012664414709</v>
       </c>
       <c r="E18" t="n">
-        <v>10.10876518886647</v>
+        <v>1.642674343190802</v>
       </c>
       <c r="F18" t="n">
-        <v>10.79168524793094</v>
+        <v>1.753648852788777</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>14.00523320465259</v>
+        <v>2.275850395756045</v>
       </c>
       <c r="D19" t="n">
-        <v>4.848466944981902</v>
+        <v>0.7878758785595591</v>
       </c>
       <c r="E19" t="n">
-        <v>10.10876518886647</v>
+        <v>1.642674343190802</v>
       </c>
       <c r="F19" t="n">
-        <v>10.79168524793094</v>
+        <v>1.753648852788777</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>8.404810571581146</v>
+        <v>1.365781717881936</v>
       </c>
       <c r="D20" t="n">
-        <v>5.176595779400585</v>
+        <v>0.8411968141525951</v>
       </c>
       <c r="E20" t="n">
-        <v>10.10876518886647</v>
+        <v>1.642674343190802</v>
       </c>
       <c r="F20" t="n">
-        <v>10.79168524793094</v>
+        <v>1.753648852788777</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>12.08395717437757</v>
+        <v>1.963643040836355</v>
       </c>
       <c r="D21" t="n">
-        <v>13.10922078525209</v>
+        <v>2.130248377603464</v>
       </c>
       <c r="E21" t="n">
-        <v>10.10876518886647</v>
+        <v>1.642674343190802</v>
       </c>
       <c r="F21" t="n">
-        <v>10.79168524793094</v>
+        <v>1.753648852788777</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>19.65706207756928</v>
+        <v>3.194272587605008</v>
       </c>
       <c r="D22" t="n">
-        <v>19.20221472298021</v>
+        <v>3.120359892484285</v>
       </c>
       <c r="E22" t="n">
-        <v>10.10876518886647</v>
+        <v>1.642674343190802</v>
       </c>
       <c r="F22" t="n">
-        <v>10.79168524793094</v>
+        <v>1.753648852788777</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>26.42480668166307</v>
+        <v>4.29403108577025</v>
       </c>
       <c r="D23" t="n">
-        <v>23.78187532813693</v>
+        <v>3.864554740822252</v>
       </c>
       <c r="E23" t="n">
-        <v>10.10876518886647</v>
+        <v>1.642674343190802</v>
       </c>
       <c r="F23" t="n">
-        <v>10.79168524793094</v>
+        <v>1.753648852788777</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>33.26027425389662</v>
+        <v>5.404794566258201</v>
       </c>
       <c r="D24" t="n">
-        <v>32.55035906915394</v>
+        <v>5.289433348737516</v>
       </c>
       <c r="E24" t="n">
-        <v>10.10876518886647</v>
+        <v>1.642674343190802</v>
       </c>
       <c r="F24" t="n">
-        <v>10.79168524793094</v>
+        <v>1.753648852788777</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>27.15525028709895</v>
+        <v>4.412728171653581</v>
       </c>
       <c r="D25" t="n">
-        <v>27.69826423015208</v>
+        <v>4.500967937399714</v>
       </c>
       <c r="E25" t="n">
-        <v>10.10876518886647</v>
+        <v>1.642674343190802</v>
       </c>
       <c r="F25" t="n">
-        <v>10.79168524793094</v>
+        <v>1.753648852788777</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>20.57185455808304</v>
+        <v>3.342926365688494</v>
       </c>
       <c r="D26" t="n">
-        <v>20.51319556711745</v>
+        <v>3.333394279656586</v>
       </c>
       <c r="E26" t="n">
-        <v>10.10876518886647</v>
+        <v>1.642674343190802</v>
       </c>
       <c r="F26" t="n">
-        <v>10.79168524793094</v>
+        <v>1.753648852788777</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>29.07891695772536</v>
+        <v>4.725324005630371</v>
       </c>
       <c r="D27" t="n">
-        <v>28.6172270895419</v>
+        <v>4.650299402050559</v>
       </c>
       <c r="E27" t="n">
-        <v>10.10876518886647</v>
+        <v>1.642674343190802</v>
       </c>
       <c r="F27" t="n">
-        <v>10.79168524793094</v>
+        <v>1.753648852788777</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
